--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-Next-80B-A3B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-Next-80B-A3B-Instruct/simple/total_votes_file.xlsx
@@ -430,13 +430,13 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="D2">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2">
         <v>17</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D3">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H3">
         <v>426</v>
